--- a/Documento 0/TablaESA_UR.xlsx
+++ b/Documento 0/TablaESA_UR.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Yn2tIUqiLbb+F9qs7wmS4bePTSCq6pYAzpeXUoz35ZM="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="NfZJCrKmVEbF87pg6+jzpZIUfy1rtnk8LMYA6WuVpnQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="183">
   <si>
     <t>Descripción</t>
   </si>
@@ -349,6 +349,18 @@
   </si>
   <si>
     <t>El jefe técnico debe poder marcar a un cliente como conflictivo con una observación visible para el técnico antes de cada visita al domicilio.</t>
+  </si>
+  <si>
+    <t>Consultando servicios activos del cliente</t>
+  </si>
+  <si>
+    <t>Permite consultar desde la ficha del cliente los servicios que tiene contratados y vigentes, con su plan, precio, fecha de inicio y estado del contrato.</t>
+  </si>
+  <si>
+    <t>Buscando clientes por criterios múltiples</t>
+  </si>
+  <si>
+    <t>Permite encontrar un cliente combinando nombre, RUT, teléfono y dirección, con coincidencia parcial, sobre el listado paginado de la empresa.</t>
   </si>
   <si>
     <t>6.- Administración, Roles y Seguridad</t>
@@ -559,7 +571,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="10">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d.m"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -606,6 +621,12 @@
       <b/>
       <sz val="9.0"/>
       <color rgb="FF7B5C00"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -658,7 +679,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border/>
     <border>
       <left style="thin">
@@ -700,26 +721,12 @@
       <bottom/>
     </border>
     <border>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF1F4E8C"/>
       </left>
       <right style="thin">
         <color rgb="FF1F4E8C"/>
       </right>
-      <top style="thin">
-        <color rgb="FF1F4E8C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF1F4E8C"/>
-      </bottom>
-    </border>
-    <border>
-      <right/>
       <top style="thin">
         <color rgb="FF1F4E8C"/>
       </top>
@@ -760,20 +767,11 @@
         <color rgb="FFAAAAAA"/>
       </bottom>
     </border>
-    <border>
-      <right/>
-      <top style="thin">
-        <color rgb="FFAAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFAAAAAA"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -786,59 +784,77 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" textRotation="90" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="10" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="7" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1056,7 +1072,7 @@
   <cols>
     <col customWidth="1" min="1" max="2" width="7.0"/>
     <col customWidth="1" min="3" max="3" width="48.43"/>
-    <col customWidth="1" min="4" max="4" width="1.86"/>
+    <col customWidth="1" min="4" max="4" width="84.29"/>
     <col customWidth="1" min="5" max="5" width="11.0"/>
     <col customWidth="1" min="6" max="6" width="10.0"/>
     <col customWidth="1" min="7" max="7" width="11.0"/>
@@ -1086,7 +1102,7 @@
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
+      <c r="D2" s="5"/>
       <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
@@ -1094,37 +1110,37 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
-      <c r="J2" s="6"/>
+      <c r="J2" s="5"/>
     </row>
     <row r="3" ht="79.5" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2"/>
@@ -1135,289 +1151,289 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="10"/>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F5" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G5" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H5" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I5" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J5" s="15">
+      <c r="E5" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F5" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G5" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H5" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I5" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J5" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F6" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G6" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H6" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I6" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J6" s="20">
+      <c r="E6" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F6" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G6" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H6" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I6" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J6" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F7" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G7" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H7" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I7" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J7" s="15">
+      <c r="E7" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G7" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H7" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I7" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J7" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F8" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G8" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H8" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I8" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J8" s="20">
+      <c r="E8" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F8" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G8" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H8" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I8" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J8" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F9" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G9" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H9" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I9" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J9" s="15">
+      <c r="E9" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F9" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G9" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H9" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I9" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J9" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="17" t="s">
+      <c r="A10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F10" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G10" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H10" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I10" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J10" s="20">
+      <c r="E10" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G10" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H10" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I10" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J10" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="12" t="s">
+      <c r="A11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F11" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G11" s="21">
+      <c r="E11" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F11" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G11" s="19">
         <v>2.0</v>
       </c>
-      <c r="H11" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I11" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J11" s="15">
+      <c r="H11" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I11" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J11" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="20">
         <v>2.0</v>
       </c>
-      <c r="G12" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H12" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I12" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J12" s="20">
+      <c r="G12" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H12" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I12" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J12" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F13" s="21">
+      <c r="E13" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F13" s="19">
         <v>2.0</v>
       </c>
-      <c r="G13" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H13" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I13" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J13" s="15">
+      <c r="G13" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I13" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J13" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="2"/>
@@ -1428,202 +1444,202 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="10"/>
+      <c r="J14" s="2"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F15" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H15" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I15" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J15" s="15">
+      <c r="E15" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F15" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H15" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I15" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J15" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="17" t="s">
+      <c r="A16" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F16" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G16" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H16" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I16" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J16" s="20">
+      <c r="E16" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F16" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H16" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I16" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J16" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="12" t="s">
+      <c r="A17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F17" s="21">
+      <c r="E17" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F17" s="19">
         <v>2.0</v>
       </c>
-      <c r="G17" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H17" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I17" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J17" s="15">
+      <c r="G17" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H17" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I17" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J17" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="17" t="s">
+      <c r="A18" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F18" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G18" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H18" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I18" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J18" s="20">
+      <c r="E18" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F18" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G18" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H18" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I18" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J18" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="12" t="s">
+      <c r="A19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F19" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G19" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H19" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I19" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J19" s="21">
+      <c r="E19" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F19" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G19" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H19" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I19" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J19" s="19">
         <v>2.0</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="17" t="s">
+      <c r="A20" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F20" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G20" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H20" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I20" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J20" s="22">
+      <c r="E20" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F20" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G20" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H20" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I20" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J20" s="20">
         <v>2.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B21" s="2"/>
@@ -1634,106 +1650,106 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="10"/>
+      <c r="J21" s="2"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="17" t="s">
+      <c r="A22" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F22" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G22" s="22">
+      <c r="E22" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F22" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G22" s="20">
         <v>2.0</v>
       </c>
-      <c r="H22" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I22" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J22" s="20">
+      <c r="H22" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I22" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J22" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F23" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G23" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H23" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I23" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J23" s="15">
+      <c r="E23" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F23" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G23" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H23" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I23" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J23" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="17" t="s">
+      <c r="A24" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E24" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F24" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G24" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H24" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I24" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J24" s="20">
+      <c r="E24" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F24" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G24" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H24" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I24" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J24" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>67</v>
       </c>
       <c r="B25" s="2"/>
@@ -1744,170 +1760,170 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="10"/>
+      <c r="J25" s="2"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="17" t="s">
+      <c r="A26" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F26" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G26" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H26" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I26" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J26" s="20">
+      <c r="E26" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F26" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G26" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H26" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I26" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J26" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" s="12" t="s">
+      <c r="A27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E27" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F27" s="21">
+      <c r="E27" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F27" s="19">
         <v>2.0</v>
       </c>
-      <c r="G27" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H27" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I27" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J27" s="15">
+      <c r="G27" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H27" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I27" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J27" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="17" t="s">
+      <c r="A28" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="E28" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F28" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G28" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H28" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I28" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J28" s="22">
+      <c r="E28" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F28" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G28" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H28" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I28" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J28" s="20">
         <v>2.0</v>
       </c>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="12" t="s">
+      <c r="A29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E29" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F29" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G29" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H29" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I29" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J29" s="21">
+      <c r="E29" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F29" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G29" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H29" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I29" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J29" s="19">
         <v>2.0</v>
       </c>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="17" t="s">
+      <c r="A30" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="E30" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F30" s="22">
+      <c r="E30" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F30" s="20">
         <v>2.0</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="20">
         <v>2.0</v>
       </c>
-      <c r="H30" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I30" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J30" s="20">
+      <c r="H30" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I30" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J30" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="8" t="s">
         <v>83</v>
       </c>
       <c r="B31" s="2"/>
@@ -1918,1040 +1934,1102 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="10"/>
+      <c r="J31" s="2"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="17" t="s">
+      <c r="A32" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F32" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G32" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H32" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I32" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J32" s="20">
+      <c r="E32" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F32" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G32" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H32" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I32" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J32" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="12" t="s">
+      <c r="A33" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F33" s="21">
+      <c r="E33" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F33" s="19">
         <v>2.0</v>
       </c>
-      <c r="G33" s="21">
+      <c r="G33" s="19">
         <v>2.0</v>
       </c>
-      <c r="H33" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I33" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J33" s="15">
+      <c r="H33" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I33" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J33" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="17" t="s">
+      <c r="A34" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="E34" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F34" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G34" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H34" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I34" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J34" s="20">
+      <c r="E34" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F34" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G34" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H34" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I34" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J34" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="12" t="s">
+      <c r="A35" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E35" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F35" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G35" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H35" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I35" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J35" s="15">
+      <c r="E35" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F35" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G35" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H35" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I35" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J35" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="17" t="s">
+      <c r="A36" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="E36" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F36" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G36" s="22">
+      <c r="E36" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F36" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G36" s="20">
         <v>2.0</v>
       </c>
-      <c r="H36" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I36" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J36" s="20">
+      <c r="H36" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I36" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J36" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="12" t="s">
+      <c r="A37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E37" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F37" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G37" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H37" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I37" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J37" s="15">
+      <c r="E37" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F37" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G37" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H37" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I37" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J37" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="17" t="s">
+      <c r="A38" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E38" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F38" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G38" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H38" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I38" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J38" s="20">
+      <c r="E38" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F38" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G38" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H38" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I38" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J38" s="18">
         <v>1.0</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="12" t="s">
+      <c r="A39" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E39" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F39" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G39" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H39" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I39" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J39" s="15">
+      <c r="E39" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F39" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G39" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H39" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I39" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J39" s="13">
         <v>1.0</v>
       </c>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B40" s="17" t="s">
+      <c r="A40" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E40" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F40" s="22">
+      <c r="E40" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F40" s="20">
         <v>2.0</v>
       </c>
-      <c r="G40" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H40" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I40" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J40" s="20">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="9" t="s">
+      <c r="G40" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H40" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I40" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J40" s="18">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.0" customHeight="1">
+      <c r="A41" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="22">
+        <v>46300.0</v>
+      </c>
+      <c r="C41" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="10"/>
+      <c r="D41" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E41" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="F41" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="G41" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="H41" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="I41" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="J41" s="25">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C42" s="18" t="s">
+      <c r="A42" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="22">
+        <v>46331.0</v>
+      </c>
+      <c r="C42" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="E42" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F42" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G42" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H42" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I42" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J42" s="20">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" s="12" t="s">
+      <c r="E42" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="F42" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="G42" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="H42" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="I42" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="J42" s="25">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+    </row>
+    <row r="44" ht="15.0" customHeight="1">
+      <c r="A44" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="C44" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="E43" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F43" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G43" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H43" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I43" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J43" s="21">
+      <c r="D44" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E44" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F44" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G44" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H44" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I44" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J44" s="18">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="45" ht="15.0" customHeight="1">
+      <c r="A45" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E45" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F45" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G45" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H45" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I45" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J45" s="19">
         <v>2.0</v>
       </c>
     </row>
-    <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="E44" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F44" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G44" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H44" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I44" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J44" s="22">
+    <row r="46" ht="15.0" customHeight="1">
+      <c r="A46" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E46" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F46" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G46" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H46" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I46" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J46" s="20">
         <v>2.0</v>
       </c>
     </row>
-    <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E45" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F45" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G45" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H45" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I45" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J45" s="21">
+    <row r="47" ht="15.0" customHeight="1">
+      <c r="A47" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F47" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G47" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H47" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I47" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J47" s="19">
         <v>2.0</v>
       </c>
     </row>
-    <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C46" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="E46" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F46" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G46" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H46" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I46" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J46" s="22">
+    <row r="48" ht="15.0" customHeight="1">
+      <c r="A48" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F48" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G48" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H48" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I48" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J48" s="20">
         <v>2.0</v>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="10"/>
-    </row>
-    <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E48" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F48" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G48" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H48" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I48" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J48" s="20">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" s="12" t="s">
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" ht="15.0" customHeight="1">
+      <c r="A50" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="C50" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="E49" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F49" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G49" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H49" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I49" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J49" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B50" s="17" t="s">
+      <c r="D50" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="E50" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F50" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G50" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H50" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I50" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J50" s="18">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="51" ht="15.0" customHeight="1">
+      <c r="A51" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="D50" s="19" t="s">
+      <c r="C51" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="E50" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F50" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G50" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H50" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I50" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J50" s="20">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" s="12" t="s">
+      <c r="D51" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="E51" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F51" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G51" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H51" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I51" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J51" s="13">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="52" ht="15.0" customHeight="1">
+      <c r="A52" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="C52" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="E51" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F51" s="21">
+      <c r="D52" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F52" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G52" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H52" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I52" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J52" s="18">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="53" ht="15.0" customHeight="1">
+      <c r="A53" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E53" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F53" s="19">
         <v>2.0</v>
       </c>
-      <c r="G51" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H51" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I51" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J51" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="E52" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F52" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G52" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H52" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I52" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J52" s="22">
+      <c r="G53" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H53" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I53" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J53" s="13">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="54" ht="15.0" customHeight="1">
+      <c r="A54" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F54" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G54" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H54" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I54" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J54" s="20">
         <v>2.0</v>
       </c>
     </row>
-    <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E53" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F53" s="21">
+    <row r="55" ht="15.0" customHeight="1">
+      <c r="A55" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E55" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F55" s="19">
         <v>2.0</v>
       </c>
-      <c r="G53" s="21">
+      <c r="G55" s="19">
         <v>2.0</v>
       </c>
-      <c r="H53" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I53" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J53" s="21">
+      <c r="H55" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I55" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J55" s="19">
         <v>2.0</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="10"/>
-    </row>
-    <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E55" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F55" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G55" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H55" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I55" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J55" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B56" s="17" t="s">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C56" s="18" t="s">
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+    </row>
+    <row r="57" ht="15.0" customHeight="1">
+      <c r="A57" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D56" s="19" t="s">
+      <c r="C57" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="E56" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F56" s="22">
+      <c r="D57" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E57" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F57" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G57" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H57" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I57" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J57" s="13">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="58" ht="15.0" customHeight="1">
+      <c r="A58" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="E58" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F58" s="20">
         <v>2.0</v>
       </c>
-      <c r="G56" s="22">
+      <c r="G58" s="20">
         <v>2.0</v>
       </c>
-      <c r="H56" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I56" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J56" s="22">
+      <c r="H58" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I58" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J58" s="20">
         <v>2.0</v>
       </c>
     </row>
-    <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E57" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F57" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G57" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H57" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I57" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J57" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C58" s="18" t="s">
+    <row r="59" ht="15.0" customHeight="1">
+      <c r="A59" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="D58" s="19" t="s">
+      <c r="C59" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E58" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F58" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G58" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H58" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I58" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J58" s="22">
+      <c r="D59" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E59" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F59" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G59" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H59" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I59" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J59" s="13">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="60" ht="15.0" customHeight="1">
+      <c r="A60" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E60" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F60" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G60" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H60" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I60" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J60" s="20">
         <v>2.0</v>
       </c>
     </row>
-    <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="E59" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F59" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G59" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H59" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I59" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J59" s="21">
+    <row r="61" ht="15.0" customHeight="1">
+      <c r="A61" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E61" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F61" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G61" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H61" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I61" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J61" s="19">
         <v>2.0</v>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="10"/>
-    </row>
-    <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="E61" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F61" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G61" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H61" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I61" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J61" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B62" s="17" t="s">
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C62" s="18" t="s">
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+    </row>
+    <row r="63" ht="15.0" customHeight="1">
+      <c r="A63" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="C63" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E62" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F62" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G62" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H62" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I62" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J62" s="20">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B63" s="12" t="s">
+      <c r="D63" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="E63" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F63" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G63" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H63" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I63" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J63" s="13">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="64" ht="15.0" customHeight="1">
+      <c r="A64" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="C64" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F63" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="G63" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="H63" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I63" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J63" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B64" s="17" t="s">
+      <c r="D64" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="E64" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F64" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="G64" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H64" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I64" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J64" s="18">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="65" ht="15.0" customHeight="1">
+      <c r="A65" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="C65" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="E64" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F64" s="22">
+      <c r="D65" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E65" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F65" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G65" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H65" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I65" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J65" s="13">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="66" ht="15.0" customHeight="1">
+      <c r="A66" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="E66" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="F66" s="20">
         <v>2.0</v>
       </c>
-      <c r="G64" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H64" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I64" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J64" s="20">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="D65" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="E65" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F65" s="21">
+      <c r="G66" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H66" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="I66" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J66" s="18">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="67" ht="15.0" customHeight="1">
+      <c r="A67" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E67" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="F67" s="19">
         <v>2.0</v>
       </c>
-      <c r="G65" s="21">
+      <c r="G67" s="19">
         <v>2.0</v>
       </c>
-      <c r="H65" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="I65" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J65" s="21">
+      <c r="H67" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="I67" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="J67" s="19">
         <v>2.0</v>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="B66" s="24"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="26"/>
-      <c r="F66" s="26"/>
-      <c r="G66" s="26"/>
-      <c r="H66" s="26"/>
-      <c r="I66" s="26"/>
-      <c r="J66" s="26"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" s="29"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="30"/>
+    </row>
     <row r="69" ht="15.75" customHeight="1"/>
     <row r="70" ht="15.75" customHeight="1"/>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3884,14 +3962,16 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A60:J60"/>
-    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A62:J62"/>
+    <mergeCell ref="A68:D68"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:J2"/>
